--- a/data/trans_orig/P16A_n_R3-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P16A_n_R3-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido cinco o más medicamentos en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido cinco o más medicamentos en las dos últimas semanas en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2842</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13212</t>
+          <t>14136</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1958</t>
+          <t>2055</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11354</t>
+          <t>12012</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6755</t>
+          <t>7092</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20465</t>
+          <t>21089</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>680800</t>
+          <t>679876</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>691170</t>
+          <t>691156</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>676997</t>
+          <t>676339</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>686393</t>
+          <t>686296</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1361898</t>
+          <t>1361274</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1375608</t>
+          <t>1375271</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,49%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>8188</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25537</t>
+          <t>25936</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13849</t>
+          <t>13599</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32855</t>
+          <t>33226</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25701</t>
+          <t>25313</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>49736</t>
+          <t>50036</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>936263</t>
+          <t>935864</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>953217</t>
+          <t>953612</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>935538</t>
+          <t>935167</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>954544</t>
+          <t>954794</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1880457</t>
+          <t>1880157</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1904492</t>
+          <t>1904880</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,69%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4669</t>
+          <t>4642</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17594</t>
+          <t>17802</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18572</t>
+          <t>20160</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40406</t>
+          <t>40032</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27461</t>
+          <t>26642</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>52360</t>
+          <t>50922</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>660915</t>
+          <t>660707</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>673840</t>
+          <t>673867</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>643435</t>
+          <t>643809</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>665269</t>
+          <t>663681</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1309990</t>
+          <t>1311428</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1334889</t>
+          <t>1335708</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,04%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11723</t>
+          <t>11824</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26444</t>
+          <t>27301</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21182</t>
+          <t>21201</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>43773</t>
+          <t>43115</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>36394</t>
+          <t>36893</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>64416</t>
+          <t>63736</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>915778</t>
+          <t>914921</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>930499</t>
+          <t>930398</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>994839</t>
+          <t>995497</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1017430</t>
+          <t>1017411</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1916418</t>
+          <t>1917098</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1944440</t>
+          <t>1943941</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,14%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>36592</t>
+          <t>36732</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>64528</t>
+          <t>62924</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>69379</t>
+          <t>71158</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>108246</t>
+          <t>107516</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>113981</t>
+          <t>113739</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>161115</t>
+          <t>160060</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3212015</t>
+          <t>3213619</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3239951</t>
+          <t>3239811</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3270951</t>
+          <t>3271681</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3309818</t>
+          <t>3308039</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6494626</t>
+          <t>6495681</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6541760</t>
+          <t>6542002</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido cinco o más medicamentos en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido cinco o más medicamentos en las dos últimas semanas en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4432</t>
+          <t>4252</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18004</t>
+          <t>16955</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22670</t>
+          <t>22075</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>45380</t>
+          <t>44780</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29460</t>
+          <t>31064</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>56401</t>
+          <t>57100</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>685465</t>
+          <t>686514</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>699037</t>
+          <t>699217</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>651670</t>
+          <t>652270</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>674380</t>
+          <t>674975</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1344118</t>
+          <t>1343419</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1371059</t>
+          <t>1369455</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,78%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6524</t>
+          <t>6620</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21913</t>
+          <t>24310</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>40319</t>
+          <t>39556</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>69061</t>
+          <t>70045</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>50313</t>
+          <t>50987</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>82938</t>
+          <t>85387</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>996034</t>
+          <t>993637</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1011423</t>
+          <t>1011327</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>963123</t>
+          <t>962139</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>991865</t>
+          <t>992628</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1967193</t>
+          <t>1964744</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1999818</t>
+          <t>1999144</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,51%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10119</t>
+          <t>9702</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31321</t>
+          <t>31265</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,7 +3381,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19629</t>
+          <t>18660</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>41391</t>
+          <t>40497</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>33628</t>
+          <t>32406</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>62721</t>
+          <t>63323</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,13%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>726302</t>
+          <t>726358</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>747504</t>
+          <t>747921</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3499,7 +3499,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>735783</t>
+          <t>736677</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>757545</t>
+          <t>758514</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1472076</t>
+          <t>1471474</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1501169</t>
+          <t>1502391</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,89%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14254</t>
+          <t>14412</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35324</t>
+          <t>34741</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48382</t>
+          <t>48610</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>81267</t>
+          <t>82916</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>68067</t>
+          <t>67351</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>103760</t>
+          <t>105666</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,28%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>912415</t>
+          <t>912998</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>933485</t>
+          <t>933327</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>970634</t>
+          <t>968985</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1003519</t>
+          <t>1003291</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1895880</t>
+          <t>1893974</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1931573</t>
+          <t>1932289</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,63%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>45861</t>
+          <t>46500</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>80691</t>
+          <t>81122</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>154178</t>
+          <t>152290</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>205263</t>
+          <t>203778</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>205742</t>
+          <t>210195</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>271287</t>
+          <t>272328</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3346088</t>
+          <t>3345657</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3380918</t>
+          <t>3380279</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3353046</t>
+          <t>3354531</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3404131</t>
+          <t>3406019</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6713801</t>
+          <t>6712760</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6779346</t>
+          <t>6774893</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>96,99%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido cinco o más medicamentos en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido cinco o más medicamentos en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8547</t>
+          <t>8714</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24236</t>
+          <t>24682</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,82 +4642,82 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
+          <t>3,66%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>33623</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>23901</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>46109</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>5,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>3,55%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>6,85%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>48424</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>36476</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>63652</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
           <t>3,59%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>33623</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>24035</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>45862</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>5,0%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>3,57%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>6,82%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>48424</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>35393</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>64764</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>3,59%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,72%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>650564</t>
+          <t>650118</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>666253</t>
+          <t>666086</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,82 +4755,82 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>96,34%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>98,71%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>634</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>639216</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>626730</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>648938</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>95,0%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>93,15%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>96,45%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>1270</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>1299215</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>1283987</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>1311163</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
           <t>96,41%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>98,73%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>634</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>639216</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>626977</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>648804</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>95,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>93,18%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>96,43%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1270</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>1299215</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>1282875</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>1312246</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>96,41%</t>
-        </is>
-      </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,29%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9378</t>
+          <t>9510</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26776</t>
+          <t>24965</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24779</t>
+          <t>24137</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50127</t>
+          <t>49310</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>37701</t>
+          <t>38894</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>67796</t>
+          <t>68942</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>995655</t>
+          <t>997466</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1013053</t>
+          <t>1012921</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>992786</t>
+          <t>993603</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1018134</t>
+          <t>1018776</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1997548</t>
+          <t>1996402</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2027643</t>
+          <t>2026450</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,12%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8158</t>
+          <t>8464</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24603</t>
+          <t>23439</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20494</t>
+          <t>20850</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42489</t>
+          <t>43556</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>33788</t>
+          <t>32887</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>60323</t>
+          <t>60845</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>734949</t>
+          <t>736113</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>751394</t>
+          <t>751088</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>742522</t>
+          <t>741455</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>764517</t>
+          <t>764161</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1484240</t>
+          <t>1483718</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1510775</t>
+          <t>1511676</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,87%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5982</t>
+          <t>5907</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19217</t>
+          <t>19623</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>40399</t>
+          <t>40269</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>70183</t>
+          <t>69198</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>48246</t>
+          <t>48738</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>81980</t>
+          <t>81621</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>918350</t>
+          <t>917944</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>931585</t>
+          <t>931660</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>973596</t>
+          <t>974581</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1003380</t>
+          <t>1003510</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1899366</t>
+          <t>1899725</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1933100</t>
+          <t>1932608</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,54%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>43049</t>
+          <t>42439</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>70937</t>
+          <t>71332</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>127474</t>
+          <t>130043</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>178651</t>
+          <t>183207</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>179161</t>
+          <t>181738</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>239935</t>
+          <t>242032</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3323413</t>
+          <t>3323018</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3351301</t>
+          <t>3351911</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3365891</t>
+          <t>3361335</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3417068</t>
+          <t>3414499</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6698957</t>
+          <t>6696860</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6759731</t>
+          <t>6757154</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,38%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido cinco o más medicamentos en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido cinco o más medicamentos en las dos últimas semanas en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>29786</t>
+          <t>29196</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>50736</t>
+          <t>49632</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>55387</t>
+          <t>55536</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>83533</t>
+          <t>82454</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>92433</t>
+          <t>93851</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>125739</t>
+          <t>125991</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,26%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>584705</t>
+          <t>585809</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>605655</t>
+          <t>606245</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>641797</t>
+          <t>642876</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>669943</t>
+          <t>669794</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1235033</t>
+          <t>1234781</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1268339</t>
+          <t>1266921</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,1%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22886</t>
+          <t>19600</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>58958</t>
+          <t>58047</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>77070</t>
+          <t>76995</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>103402</t>
+          <t>103205</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>87857</t>
+          <t>85688</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>157142</t>
+          <t>154697</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,19%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1133906</t>
+          <t>1134817</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1169978</t>
+          <t>1173264</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>855249</t>
+          <t>855446</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>881581</t>
+          <t>881656</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1994374</t>
+          <t>1996819</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2063659</t>
+          <t>2065828</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>96,02%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18560</t>
+          <t>19252</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37957</t>
+          <t>37794</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26560</t>
+          <t>24888</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>71773</t>
+          <t>71006</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>50720</t>
+          <t>51878</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>96311</t>
+          <t>96184</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,87%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>666723</t>
+          <t>666886</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>686120</t>
+          <t>685428</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>861593</t>
+          <t>862360</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>906806</t>
+          <t>908478</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1541735</t>
+          <t>1541862</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1587326</t>
+          <t>1586168</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,83%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39213</t>
+          <t>38816</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>62618</t>
+          <t>62722</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>94759</t>
+          <t>93792</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>140146</t>
+          <t>141707</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>145669</t>
+          <t>141084</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>194190</t>
+          <t>193085</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,55%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>864213</t>
+          <t>864109</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>887618</t>
+          <t>888015</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>954786</t>
+          <t>953225</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1000173</t>
+          <t>1001140</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>87,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1827573</t>
+          <t>1828678</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1876094</t>
+          <t>1880679</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>93,02%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>123430</t>
+          <t>122552</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>183887</t>
+          <t>181536</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>264499</t>
+          <t>266250</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>364092</t>
+          <t>365936</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>421523</t>
+          <t>415423</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>536767</t>
+          <t>533785</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,44%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3275930</t>
+          <t>3278281</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3336387</t>
+          <t>3337265</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3348188</t>
+          <t>3346344</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3447781</t>
+          <t>3446030</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6635330</t>
+          <t>6638312</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6750574</t>
+          <t>6756674</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,21%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A_n_R3-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P16A_n_R3-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2832</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14136</t>
+          <t>13273</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2055</t>
+          <t>2107</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12012</t>
+          <t>12701</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7092</t>
+          <t>6827</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21089</t>
+          <t>21263</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>679876</t>
+          <t>680739</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>691156</t>
+          <t>691180</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>676339</t>
+          <t>675650</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>686296</t>
+          <t>686244</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1361274</t>
+          <t>1361100</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1375271</t>
+          <t>1375536</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,51%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8188</t>
+          <t>8317</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25936</t>
+          <t>24066</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13599</t>
+          <t>13732</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33226</t>
+          <t>32700</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25313</t>
+          <t>25605</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>50036</t>
+          <t>50505</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>935864</t>
+          <t>937734</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>953612</t>
+          <t>953483</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>935167</t>
+          <t>935693</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>954794</t>
+          <t>954661</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1880157</t>
+          <t>1879688</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1904880</t>
+          <t>1904588</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,67%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4642</t>
+          <t>4635</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17802</t>
+          <t>18046</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20160</t>
+          <t>19415</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40032</t>
+          <t>39400</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26642</t>
+          <t>27371</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>50922</t>
+          <t>51012</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>660707</t>
+          <t>660463</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>673867</t>
+          <t>673874</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>643809</t>
+          <t>644441</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>663681</t>
+          <t>664426</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1311428</t>
+          <t>1311338</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1335708</t>
+          <t>1334979</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>97,99%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11824</t>
+          <t>11728</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27301</t>
+          <t>26604</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21201</t>
+          <t>21141</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>43115</t>
+          <t>43654</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>36893</t>
+          <t>37329</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>63736</t>
+          <t>64782</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>914921</t>
+          <t>915618</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>930398</t>
+          <t>930494</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>995497</t>
+          <t>994958</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1017411</t>
+          <t>1017471</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1917098</t>
+          <t>1916052</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1943941</t>
+          <t>1943505</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,12%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>36732</t>
+          <t>36699</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>62924</t>
+          <t>66042</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>71158</t>
+          <t>71073</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>107516</t>
+          <t>109134</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>113739</t>
+          <t>114323</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>160060</t>
+          <t>159065</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3213619</t>
+          <t>3210501</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3239811</t>
+          <t>3239844</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3271681</t>
+          <t>3270063</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3308039</t>
+          <t>3308124</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6495681</t>
+          <t>6496676</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6542002</t>
+          <t>6541418</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,28%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4252</t>
+          <t>4297</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16955</t>
+          <t>17658</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22075</t>
+          <t>22152</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>44780</t>
+          <t>45096</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>31064</t>
+          <t>30695</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>57100</t>
+          <t>55630</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,97%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>686514</t>
+          <t>685811</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>699217</t>
+          <t>699172</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>652270</t>
+          <t>651954</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>674975</t>
+          <t>674898</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1343419</t>
+          <t>1344889</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1369455</t>
+          <t>1369824</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,81%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6620</t>
+          <t>5706</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24310</t>
+          <t>21175</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>39556</t>
+          <t>39905</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>70045</t>
+          <t>67180</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>50987</t>
+          <t>50571</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>85387</t>
+          <t>84855</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>993637</t>
+          <t>996772</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1011327</t>
+          <t>1012241</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>962139</t>
+          <t>965004</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>992628</t>
+          <t>992279</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1964744</t>
+          <t>1965276</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1999144</t>
+          <t>1999560</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,53%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9702</t>
+          <t>9510</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31265</t>
+          <t>31452</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18660</t>
+          <t>18943</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40497</t>
+          <t>40252</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>32406</t>
+          <t>33122</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>63323</t>
+          <t>63302</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>726358</t>
+          <t>726171</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>747921</t>
+          <t>748113</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>736677</t>
+          <t>736922</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>758514</t>
+          <t>758231</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1471474</t>
+          <t>1471495</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1502391</t>
+          <t>1501675</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,84%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14412</t>
+          <t>13916</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34741</t>
+          <t>36098</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48610</t>
+          <t>48503</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>82916</t>
+          <t>79177</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>67351</t>
+          <t>67820</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>105666</t>
+          <t>104571</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,23%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>912998</t>
+          <t>911641</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>933327</t>
+          <t>933823</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>968985</t>
+          <t>972724</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1003291</t>
+          <t>1003398</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1893974</t>
+          <t>1895069</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1932289</t>
+          <t>1931820</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,61%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>46500</t>
+          <t>46738</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>81122</t>
+          <t>84898</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>152290</t>
+          <t>151751</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>203778</t>
+          <t>205189</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>210195</t>
+          <t>209642</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>272328</t>
+          <t>270618</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,87%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3345657</t>
+          <t>3341881</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3380279</t>
+          <t>3380041</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3354531</t>
+          <t>3353120</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3406019</t>
+          <t>3406558</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6712760</t>
+          <t>6714470</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6774893</t>
+          <t>6775446</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,0%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8714</t>
+          <t>9259</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24682</t>
+          <t>23288</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23901</t>
+          <t>23441</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>46109</t>
+          <t>46792</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>36476</t>
+          <t>36498</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>63652</t>
+          <t>63397</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4717,7 +4717,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,7%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>650118</t>
+          <t>651512</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>666086</t>
+          <t>665541</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>626730</t>
+          <t>626047</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>648938</t>
+          <t>649398</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1283987</t>
+          <t>1284242</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1311163</t>
+          <t>1311141</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9510</t>
+          <t>9170</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24965</t>
+          <t>24756</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24137</t>
+          <t>23662</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>49310</t>
+          <t>49021</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>38894</t>
+          <t>36875</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>68942</t>
+          <t>68574</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>997466</t>
+          <t>997675</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1012921</t>
+          <t>1013261</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>993603</t>
+          <t>993892</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1018776</t>
+          <t>1019251</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1996402</t>
+          <t>1996770</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2026450</t>
+          <t>2028469</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,21%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8464</t>
+          <t>8124</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23439</t>
+          <t>23595</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20850</t>
+          <t>22132</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>43556</t>
+          <t>45562</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>32887</t>
+          <t>33057</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>60845</t>
+          <t>61636</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>736113</t>
+          <t>735957</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>751088</t>
+          <t>751428</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>741455</t>
+          <t>739449</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>764161</t>
+          <t>762879</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1483718</t>
+          <t>1482927</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1511676</t>
+          <t>1511506</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,86%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5907</t>
+          <t>6010</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19623</t>
+          <t>20282</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>40269</t>
+          <t>39237</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>69198</t>
+          <t>70744</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>48738</t>
+          <t>49080</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>81621</t>
+          <t>82301</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>917944</t>
+          <t>917285</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>931660</t>
+          <t>931557</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>974581</t>
+          <t>973035</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1003510</t>
+          <t>1004542</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1899725</t>
+          <t>1899045</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1932608</t>
+          <t>1932266</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,52%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>42439</t>
+          <t>41897</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>71332</t>
+          <t>72025</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>130043</t>
+          <t>129772</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>183207</t>
+          <t>177696</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>181738</t>
+          <t>182546</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>242032</t>
+          <t>241787</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3323018</t>
+          <t>3322325</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3351911</t>
+          <t>3352453</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3361335</t>
+          <t>3366846</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3414499</t>
+          <t>3414770</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6696860</t>
+          <t>6697105</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6757154</t>
+          <t>6756346</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,37%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>38620</t>
+          <t>41442</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>29196</t>
+          <t>31570</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>49632</t>
+          <t>54324</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>70552</t>
+          <t>75259</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>55536</t>
+          <t>64259</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>82454</t>
+          <t>88225</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>109172</t>
+          <t>116701</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>93851</t>
+          <t>101996</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>125991</t>
+          <t>134875</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,47%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>596821</t>
+          <t>649268</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>585809</t>
+          <t>636386</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>606245</t>
+          <t>659140</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>654778</t>
+          <t>658921</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>642876</t>
+          <t>645955</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>669794</t>
+          <t>669921</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1251600</t>
+          <t>1308188</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1234781</t>
+          <t>1290014</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1266921</t>
+          <t>1322893</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>92,84%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>41727</t>
+          <t>44066</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19600</t>
+          <t>34155</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>58047</t>
+          <t>57054</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>89673</t>
+          <t>97920</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>76995</t>
+          <t>85389</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>103205</t>
+          <t>113036</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>131400</t>
+          <t>141986</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>85688</t>
+          <t>124120</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>154697</t>
+          <t>161198</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,6%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1151137</t>
+          <t>1004851</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1134817</t>
+          <t>991863</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1173264</t>
+          <t>1014762</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>868978</t>
+          <t>973554</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>855446</t>
+          <t>958438</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>881656</t>
+          <t>986085</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2020116</t>
+          <t>1978405</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1996819</t>
+          <t>1959193</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2065828</t>
+          <t>1996271</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>94,15%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>26716</t>
+          <t>29952</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19252</t>
+          <t>20803</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37794</t>
+          <t>42194</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>51157</t>
+          <t>57743</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24888</t>
+          <t>46166</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>71006</t>
+          <t>69906</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>77873</t>
+          <t>87695</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>51878</t>
+          <t>72781</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>96184</t>
+          <t>105513</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,53%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>677964</t>
+          <t>773121</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>666886</t>
+          <t>760879</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>685428</t>
+          <t>782270</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>882209</t>
+          <t>754516</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>862360</t>
+          <t>742353</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>908478</t>
+          <t>766093</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1560173</t>
+          <t>1527637</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1541862</t>
+          <t>1509819</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1586168</t>
+          <t>1542551</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>95,49%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>49474</t>
+          <t>51955</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38816</t>
+          <t>40784</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>62722</t>
+          <t>65387</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>118423</t>
+          <t>125692</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>93792</t>
+          <t>110179</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>141707</t>
+          <t>144143</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>167897</t>
+          <t>177647</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>141084</t>
+          <t>157499</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>193085</t>
+          <t>198936</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,43%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>877357</t>
+          <t>938107</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>864109</t>
+          <t>924675</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>888015</t>
+          <t>949278</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>976509</t>
+          <t>993349</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>953225</t>
+          <t>974898</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1001140</t>
+          <t>1008862</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>88,77%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1853866</t>
+          <t>1931457</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1828678</t>
+          <t>1910168</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1880679</t>
+          <t>1951605</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>92,53%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>156537</t>
+          <t>167415</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>122552</t>
+          <t>146648</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>181536</t>
+          <t>190405</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>329805</t>
+          <t>356614</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>266250</t>
+          <t>331277</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>365936</t>
+          <t>390470</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>486342</t>
+          <t>524028</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>415423</t>
+          <t>488369</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>533785</t>
+          <t>561122</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,72%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3303280</t>
+          <t>3365347</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3278281</t>
+          <t>3342357</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3337265</t>
+          <t>3386114</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3382475</t>
+          <t>3380340</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3346344</t>
+          <t>3346484</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3446030</t>
+          <t>3405677</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6685755</t>
+          <t>6745688</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6638312</t>
+          <t>6708594</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6756674</t>
+          <t>6781347</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>93,28%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
